--- a/InputData/plcy-schd/FY/FY Future Years.xlsx
+++ b/InputData/plcy-schd/FY/FY Future Years.xlsx
@@ -1080,4 +1080,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A0BD15E-411A-4F4E-9DA6-E785C34043CF}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E033D5BF-6F61-4784-8082-DA118F405E03}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32FD28B5-58AD-4BE5-9CC6-E5DB2D3528F2}"/>
 </file>
--- a/InputData/plcy-schd/FY/FY Future Years.xlsx
+++ b/InputData/plcy-schd/FY/FY Future Years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\plcy-schd\FY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\SouthKorea EPS\InputData\plcy-schd\FY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A11848-89A1-46A2-AED1-E86E1643D610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2F8DCD-7B25-447C-927A-DB2A326E1CC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
+    <workbookView xWindow="1536" yWindow="1296" windowWidth="19944" windowHeight="13104" activeTab="1" xr2:uid="{70679913-52CE-4866-92D3-04053F7F27F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>FY Future Years</t>
   </si>
@@ -52,6 +52,246 @@
   </si>
   <si>
     <t>FutureYear</t>
+  </si>
+  <si>
+    <t>Year2021</t>
+  </si>
+  <si>
+    <t>Year2022</t>
+  </si>
+  <si>
+    <t>Year2023</t>
+  </si>
+  <si>
+    <t>Year2024</t>
+  </si>
+  <si>
+    <t>Year2025</t>
+  </si>
+  <si>
+    <t>Year2026</t>
+  </si>
+  <si>
+    <t>Year2027</t>
+  </si>
+  <si>
+    <t>Year2028</t>
+  </si>
+  <si>
+    <t>Year2029</t>
+  </si>
+  <si>
+    <t>Year2030</t>
+  </si>
+  <si>
+    <t>Year2031</t>
+  </si>
+  <si>
+    <t>Year2032</t>
+  </si>
+  <si>
+    <t>Year2033</t>
+  </si>
+  <si>
+    <t>Year2034</t>
+  </si>
+  <si>
+    <t>Year2035</t>
+  </si>
+  <si>
+    <t>Year2036</t>
+  </si>
+  <si>
+    <t>Year2037</t>
+  </si>
+  <si>
+    <t>Year2038</t>
+  </si>
+  <si>
+    <t>Year2039</t>
+  </si>
+  <si>
+    <t>Year2040</t>
+  </si>
+  <si>
+    <t>Year2041</t>
+  </si>
+  <si>
+    <t>Year2042</t>
+  </si>
+  <si>
+    <t>Year2043</t>
+  </si>
+  <si>
+    <t>Year2044</t>
+  </si>
+  <si>
+    <t>Year2045</t>
+  </si>
+  <si>
+    <t>Year2046</t>
+  </si>
+  <si>
+    <t>Year2047</t>
+  </si>
+  <si>
+    <t>Year2048</t>
+  </si>
+  <si>
+    <t>Year2049</t>
+  </si>
+  <si>
+    <t>Year2050</t>
+  </si>
+  <si>
+    <t>Year2051</t>
+  </si>
+  <si>
+    <t>Year2052</t>
+  </si>
+  <si>
+    <t>Year2053</t>
+  </si>
+  <si>
+    <t>Year2054</t>
+  </si>
+  <si>
+    <t>Year2055</t>
+  </si>
+  <si>
+    <t>Year2056</t>
+  </si>
+  <si>
+    <t>Year2057</t>
+  </si>
+  <si>
+    <t>Year2058</t>
+  </si>
+  <si>
+    <t>Year2059</t>
+  </si>
+  <si>
+    <t>Year2060</t>
+  </si>
+  <si>
+    <t>Year2061</t>
+  </si>
+  <si>
+    <t>Year2062</t>
+  </si>
+  <si>
+    <t>Year2063</t>
+  </si>
+  <si>
+    <t>Year2064</t>
+  </si>
+  <si>
+    <t>Year2065</t>
+  </si>
+  <si>
+    <t>Year2066</t>
+  </si>
+  <si>
+    <t>Year2067</t>
+  </si>
+  <si>
+    <t>Year2068</t>
+  </si>
+  <si>
+    <t>Year2069</t>
+  </si>
+  <si>
+    <t>Year2070</t>
+  </si>
+  <si>
+    <t>Year2071</t>
+  </si>
+  <si>
+    <t>Year2072</t>
+  </si>
+  <si>
+    <t>Year2073</t>
+  </si>
+  <si>
+    <t>Year2074</t>
+  </si>
+  <si>
+    <t>Year2075</t>
+  </si>
+  <si>
+    <t>Year2076</t>
+  </si>
+  <si>
+    <t>Year2077</t>
+  </si>
+  <si>
+    <t>Year2078</t>
+  </si>
+  <si>
+    <t>Year2079</t>
+  </si>
+  <si>
+    <t>Year2080</t>
+  </si>
+  <si>
+    <t>Year2081</t>
+  </si>
+  <si>
+    <t>Year2082</t>
+  </si>
+  <si>
+    <t>Year2083</t>
+  </si>
+  <si>
+    <t>Year2084</t>
+  </si>
+  <si>
+    <t>Year2085</t>
+  </si>
+  <si>
+    <t>Year2086</t>
+  </si>
+  <si>
+    <t>Year2087</t>
+  </si>
+  <si>
+    <t>Year2088</t>
+  </si>
+  <si>
+    <t>Year2089</t>
+  </si>
+  <si>
+    <t>Year2090</t>
+  </si>
+  <si>
+    <t>Year2091</t>
+  </si>
+  <si>
+    <t>Year2092</t>
+  </si>
+  <si>
+    <t>Year2093</t>
+  </si>
+  <si>
+    <t>Year2094</t>
+  </si>
+  <si>
+    <t>Year2095</t>
+  </si>
+  <si>
+    <t>Year2096</t>
+  </si>
+  <si>
+    <t>Year2097</t>
+  </si>
+  <si>
+    <t>Year2098</t>
+  </si>
+  <si>
+    <t>Year2099</t>
+  </si>
+  <si>
+    <t>Year2100</t>
   </si>
 </sst>
 </file>
@@ -440,19 +680,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6602441D-D56C-41AD-B87E-E90087615EB8}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -460,7 +700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
@@ -476,602 +716,522 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA74B36-1D0A-45A2-9167-2B70446AECC4}">
   <dimension ref="A1:A100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="str">
-        <f>"Year"&amp;About!A8</f>
-        <v>Year2021</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <f>IF(About!$A$8+ROW(A1)&gt;2100,"","Year"&amp;About!$A$8+ROW(A1))</f>
-        <v>Year2022</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="str">
-        <f>IF(About!$A$8+ROW(A2)&gt;2100,"","Year"&amp;About!$A$8+ROW(A2))</f>
-        <v>Year2023</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
-        <f>IF(About!$A$8+ROW(A3)&gt;2100,"","Year"&amp;About!$A$8+ROW(A3))</f>
-        <v>Year2024</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <f>IF(About!$A$8+ROW(A4)&gt;2100,"","Year"&amp;About!$A$8+ROW(A4))</f>
-        <v>Year2025</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
-        <f>IF(About!$A$8+ROW(A5)&gt;2100,"","Year"&amp;About!$A$8+ROW(A5))</f>
-        <v>Year2026</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
-        <f>IF(About!$A$8+ROW(A6)&gt;2100,"","Year"&amp;About!$A$8+ROW(A6))</f>
-        <v>Year2027</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
-        <f>IF(About!$A$8+ROW(A7)&gt;2100,"","Year"&amp;About!$A$8+ROW(A7))</f>
-        <v>Year2028</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
-        <f>IF(About!$A$8+ROW(A8)&gt;2100,"","Year"&amp;About!$A$8+ROW(A8))</f>
-        <v>Year2029</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
-        <f>IF(About!$A$8+ROW(A9)&gt;2100,"","Year"&amp;About!$A$8+ROW(A9))</f>
-        <v>Year2030</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="str">
-        <f>IF(About!$A$8+ROW(A10)&gt;2100,"","Year"&amp;About!$A$8+ROW(A10))</f>
-        <v>Year2031</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
-        <f>IF(About!$A$8+ROW(A11)&gt;2100,"","Year"&amp;About!$A$8+ROW(A11))</f>
-        <v>Year2032</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="str">
-        <f>IF(About!$A$8+ROW(A12)&gt;2100,"","Year"&amp;About!$A$8+ROW(A12))</f>
-        <v>Year2033</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
-        <f>IF(About!$A$8+ROW(A13)&gt;2100,"","Year"&amp;About!$A$8+ROW(A13))</f>
-        <v>Year2034</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="str">
-        <f>IF(About!$A$8+ROW(A14)&gt;2100,"","Year"&amp;About!$A$8+ROW(A14))</f>
-        <v>Year2035</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="str">
-        <f>IF(About!$A$8+ROW(A15)&gt;2100,"","Year"&amp;About!$A$8+ROW(A15))</f>
-        <v>Year2036</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="str">
-        <f>IF(About!$A$8+ROW(A16)&gt;2100,"","Year"&amp;About!$A$8+ROW(A16))</f>
-        <v>Year2037</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="str">
-        <f>IF(About!$A$8+ROW(A17)&gt;2100,"","Year"&amp;About!$A$8+ROW(A17))</f>
-        <v>Year2038</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="str">
-        <f>IF(About!$A$8+ROW(A18)&gt;2100,"","Year"&amp;About!$A$8+ROW(A18))</f>
-        <v>Year2039</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="str">
-        <f>IF(About!$A$8+ROW(A19)&gt;2100,"","Year"&amp;About!$A$8+ROW(A19))</f>
-        <v>Year2040</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="str">
-        <f>IF(About!$A$8+ROW(A20)&gt;2100,"","Year"&amp;About!$A$8+ROW(A20))</f>
-        <v>Year2041</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="str">
-        <f>IF(About!$A$8+ROW(A21)&gt;2100,"","Year"&amp;About!$A$8+ROW(A21))</f>
-        <v>Year2042</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="str">
-        <f>IF(About!$A$8+ROW(A22)&gt;2100,"","Year"&amp;About!$A$8+ROW(A22))</f>
-        <v>Year2043</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="str">
-        <f>IF(About!$A$8+ROW(A23)&gt;2100,"","Year"&amp;About!$A$8+ROW(A23))</f>
-        <v>Year2044</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="str">
-        <f>IF(About!$A$8+ROW(A24)&gt;2100,"","Year"&amp;About!$A$8+ROW(A24))</f>
-        <v>Year2045</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="str">
-        <f>IF(About!$A$8+ROW(A25)&gt;2100,"","Year"&amp;About!$A$8+ROW(A25))</f>
-        <v>Year2046</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="str">
-        <f>IF(About!$A$8+ROW(A26)&gt;2100,"","Year"&amp;About!$A$8+ROW(A26))</f>
-        <v>Year2047</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="str">
-        <f>IF(About!$A$8+ROW(A27)&gt;2100,"","Year"&amp;About!$A$8+ROW(A27))</f>
-        <v>Year2048</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="str">
-        <f>IF(About!$A$8+ROW(A28)&gt;2100,"","Year"&amp;About!$A$8+ROW(A28))</f>
-        <v>Year2049</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="str">
-        <f>IF(About!$A$8+ROW(A29)&gt;2100,"","Year"&amp;About!$A$8+ROW(A29))</f>
-        <v>Year2050</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="str">
-        <f>IF(About!$A$8+ROW(A30)&gt;2100,"","Year"&amp;About!$A$8+ROW(A30))</f>
-        <v>Year2051</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="str">
-        <f>IF(About!$A$8+ROW(A31)&gt;2100,"","Year"&amp;About!$A$8+ROW(A31))</f>
-        <v>Year2052</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="str">
-        <f>IF(About!$A$8+ROW(A32)&gt;2100,"","Year"&amp;About!$A$8+ROW(A32))</f>
-        <v>Year2053</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="str">
-        <f>IF(About!$A$8+ROW(A33)&gt;2100,"","Year"&amp;About!$A$8+ROW(A33))</f>
-        <v>Year2054</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="str">
-        <f>IF(About!$A$8+ROW(A34)&gt;2100,"","Year"&amp;About!$A$8+ROW(A34))</f>
-        <v>Year2055</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="str">
-        <f>IF(About!$A$8+ROW(A35)&gt;2100,"","Year"&amp;About!$A$8+ROW(A35))</f>
-        <v>Year2056</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="str">
-        <f>IF(About!$A$8+ROW(A36)&gt;2100,"","Year"&amp;About!$A$8+ROW(A36))</f>
-        <v>Year2057</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="str">
-        <f>IF(About!$A$8+ROW(A37)&gt;2100,"","Year"&amp;About!$A$8+ROW(A37))</f>
-        <v>Year2058</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="str">
-        <f>IF(About!$A$8+ROW(A38)&gt;2100,"","Year"&amp;About!$A$8+ROW(A38))</f>
-        <v>Year2059</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="str">
-        <f>IF(About!$A$8+ROW(A39)&gt;2100,"","Year"&amp;About!$A$8+ROW(A39))</f>
-        <v>Year2060</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="str">
-        <f>IF(About!$A$8+ROW(A40)&gt;2100,"","Year"&amp;About!$A$8+ROW(A40))</f>
-        <v>Year2061</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="str">
-        <f>IF(About!$A$8+ROW(A41)&gt;2100,"","Year"&amp;About!$A$8+ROW(A41))</f>
-        <v>Year2062</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="str">
-        <f>IF(About!$A$8+ROW(A42)&gt;2100,"","Year"&amp;About!$A$8+ROW(A42))</f>
-        <v>Year2063</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="str">
-        <f>IF(About!$A$8+ROW(A43)&gt;2100,"","Year"&amp;About!$A$8+ROW(A43))</f>
-        <v>Year2064</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="str">
-        <f>IF(About!$A$8+ROW(A44)&gt;2100,"","Year"&amp;About!$A$8+ROW(A44))</f>
-        <v>Year2065</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="str">
-        <f>IF(About!$A$8+ROW(A45)&gt;2100,"","Year"&amp;About!$A$8+ROW(A45))</f>
-        <v>Year2066</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="str">
-        <f>IF(About!$A$8+ROW(A46)&gt;2100,"","Year"&amp;About!$A$8+ROW(A46))</f>
-        <v>Year2067</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="str">
-        <f>IF(About!$A$8+ROW(A47)&gt;2100,"","Year"&amp;About!$A$8+ROW(A47))</f>
-        <v>Year2068</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="str">
-        <f>IF(About!$A$8+ROW(A48)&gt;2100,"","Year"&amp;About!$A$8+ROW(A48))</f>
-        <v>Year2069</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="str">
-        <f>IF(About!$A$8+ROW(A49)&gt;2100,"","Year"&amp;About!$A$8+ROW(A49))</f>
-        <v>Year2070</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="str">
-        <f>IF(About!$A$8+ROW(A50)&gt;2100,"","Year"&amp;About!$A$8+ROW(A50))</f>
-        <v>Year2071</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="str">
-        <f>IF(About!$A$8+ROW(A51)&gt;2100,"","Year"&amp;About!$A$8+ROW(A51))</f>
-        <v>Year2072</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="str">
-        <f>IF(About!$A$8+ROW(A52)&gt;2100,"","Year"&amp;About!$A$8+ROW(A52))</f>
-        <v>Year2073</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="str">
-        <f>IF(About!$A$8+ROW(A53)&gt;2100,"","Year"&amp;About!$A$8+ROW(A53))</f>
-        <v>Year2074</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="str">
-        <f>IF(About!$A$8+ROW(A54)&gt;2100,"","Year"&amp;About!$A$8+ROW(A54))</f>
-        <v>Year2075</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="str">
-        <f>IF(About!$A$8+ROW(A55)&gt;2100,"","Year"&amp;About!$A$8+ROW(A55))</f>
-        <v>Year2076</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="str">
-        <f>IF(About!$A$8+ROW(A56)&gt;2100,"","Year"&amp;About!$A$8+ROW(A56))</f>
-        <v>Year2077</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="str">
-        <f>IF(About!$A$8+ROW(A57)&gt;2100,"","Year"&amp;About!$A$8+ROW(A57))</f>
-        <v>Year2078</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="str">
-        <f>IF(About!$A$8+ROW(A58)&gt;2100,"","Year"&amp;About!$A$8+ROW(A58))</f>
-        <v>Year2079</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="str">
-        <f>IF(About!$A$8+ROW(A59)&gt;2100,"","Year"&amp;About!$A$8+ROW(A59))</f>
-        <v>Year2080</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="str">
-        <f>IF(About!$A$8+ROW(A60)&gt;2100,"","Year"&amp;About!$A$8+ROW(A60))</f>
-        <v>Year2081</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="str">
-        <f>IF(About!$A$8+ROW(A61)&gt;2100,"","Year"&amp;About!$A$8+ROW(A61))</f>
-        <v>Year2082</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="str">
-        <f>IF(About!$A$8+ROW(A62)&gt;2100,"","Year"&amp;About!$A$8+ROW(A62))</f>
-        <v>Year2083</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="str">
-        <f>IF(About!$A$8+ROW(A63)&gt;2100,"","Year"&amp;About!$A$8+ROW(A63))</f>
-        <v>Year2084</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="str">
-        <f>IF(About!$A$8+ROW(A64)&gt;2100,"","Year"&amp;About!$A$8+ROW(A64))</f>
-        <v>Year2085</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="str">
-        <f>IF(About!$A$8+ROW(A65)&gt;2100,"","Year"&amp;About!$A$8+ROW(A65))</f>
-        <v>Year2086</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="str">
-        <f>IF(About!$A$8+ROW(A66)&gt;2100,"","Year"&amp;About!$A$8+ROW(A66))</f>
-        <v>Year2087</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="str">
-        <f>IF(About!$A$8+ROW(A67)&gt;2100,"","Year"&amp;About!$A$8+ROW(A67))</f>
-        <v>Year2088</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="str">
-        <f>IF(About!$A$8+ROW(A68)&gt;2100,"","Year"&amp;About!$A$8+ROW(A68))</f>
-        <v>Year2089</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="str">
-        <f>IF(About!$A$8+ROW(A69)&gt;2100,"","Year"&amp;About!$A$8+ROW(A69))</f>
-        <v>Year2090</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="str">
-        <f>IF(About!$A$8+ROW(A70)&gt;2100,"","Year"&amp;About!$A$8+ROW(A70))</f>
-        <v>Year2091</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="str">
-        <f>IF(About!$A$8+ROW(A71)&gt;2100,"","Year"&amp;About!$A$8+ROW(A71))</f>
-        <v>Year2092</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="str">
-        <f>IF(About!$A$8+ROW(A72)&gt;2100,"","Year"&amp;About!$A$8+ROW(A72))</f>
-        <v>Year2093</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="str">
-        <f>IF(About!$A$8+ROW(A73)&gt;2100,"","Year"&amp;About!$A$8+ROW(A73))</f>
-        <v>Year2094</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="str">
-        <f>IF(About!$A$8+ROW(A74)&gt;2100,"","Year"&amp;About!$A$8+ROW(A74))</f>
-        <v>Year2095</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="str">
-        <f>IF(About!$A$8+ROW(A75)&gt;2100,"","Year"&amp;About!$A$8+ROW(A75))</f>
-        <v>Year2096</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="str">
-        <f>IF(About!$A$8+ROW(A76)&gt;2100,"","Year"&amp;About!$A$8+ROW(A76))</f>
-        <v>Year2097</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="str">
-        <f>IF(About!$A$8+ROW(A77)&gt;2100,"","Year"&amp;About!$A$8+ROW(A77))</f>
-        <v>Year2098</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="str">
-        <f>IF(About!$A$8+ROW(A78)&gt;2100,"","Year"&amp;About!$A$8+ROW(A78))</f>
-        <v>Year2099</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="str">
-        <f>IF(About!$A$8+ROW(A79)&gt;2100,"","Year"&amp;About!$A$8+ROW(A79))</f>
-        <v>Year2100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="str">
         <f>IF(About!$A$8+ROW(A80)&gt;2100,"","Year"&amp;About!$A$8+ROW(A80))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="str">
         <f>IF(About!$A$8+ROW(A81)&gt;2100,"","Year"&amp;About!$A$8+ROW(A81))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="str">
         <f>IF(About!$A$8+ROW(A82)&gt;2100,"","Year"&amp;About!$A$8+ROW(A82))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="str">
         <f>IF(About!$A$8+ROW(A83)&gt;2100,"","Year"&amp;About!$A$8+ROW(A83))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="str">
         <f>IF(About!$A$8+ROW(A84)&gt;2100,"","Year"&amp;About!$A$8+ROW(A84))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="str">
         <f>IF(About!$A$8+ROW(A85)&gt;2100,"","Year"&amp;About!$A$8+ROW(A85))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="str">
         <f>IF(About!$A$8+ROW(A86)&gt;2100,"","Year"&amp;About!$A$8+ROW(A86))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="str">
         <f>IF(About!$A$8+ROW(A87)&gt;2100,"","Year"&amp;About!$A$8+ROW(A87))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="str">
         <f>IF(About!$A$8+ROW(A88)&gt;2100,"","Year"&amp;About!$A$8+ROW(A88))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="str">
         <f>IF(About!$A$8+ROW(A89)&gt;2100,"","Year"&amp;About!$A$8+ROW(A89))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="str">
         <f>IF(About!$A$8+ROW(A90)&gt;2100,"","Year"&amp;About!$A$8+ROW(A90))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="str">
         <f>IF(About!$A$8+ROW(A91)&gt;2100,"","Year"&amp;About!$A$8+ROW(A91))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="str">
         <f>IF(About!$A$8+ROW(A92)&gt;2100,"","Year"&amp;About!$A$8+ROW(A92))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="str">
         <f>IF(About!$A$8+ROW(A93)&gt;2100,"","Year"&amp;About!$A$8+ROW(A93))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="str">
         <f>IF(About!$A$8+ROW(A94)&gt;2100,"","Year"&amp;About!$A$8+ROW(A94))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="str">
         <f>IF(About!$A$8+ROW(A95)&gt;2100,"","Year"&amp;About!$A$8+ROW(A95))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="str">
         <f>IF(About!$A$8+ROW(A96)&gt;2100,"","Year"&amp;About!$A$8+ROW(A96))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="str">
         <f>IF(About!$A$8+ROW(A97)&gt;2100,"","Year"&amp;About!$A$8+ROW(A97))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="str">
         <f>IF(About!$A$8+ROW(A98)&gt;2100,"","Year"&amp;About!$A$8+ROW(A98))</f>
         <v/>
@@ -1083,6 +1243,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1226,29 +1401,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A0BD15E-411A-4F4E-9DA6-E785C34043CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32FD28B5-58AD-4BE5-9CC6-E5DB2D3528F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E033D5BF-6F61-4784-8082-DA118F405E03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E033D5BF-6F61-4784-8082-DA118F405E03}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32FD28B5-58AD-4BE5-9CC6-E5DB2D3528F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A0BD15E-411A-4F4E-9DA6-E785C34043CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>